--- a/pensum/ma05/MA05_Markedssegmentering_Oppgaver_v6.xlsx
+++ b/pensum/ma05/MA05_Markedssegmentering_Oppgaver_v6.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="179">
   <si>
     <t xml:space="preserve">Markedssegmentering: oppgaver til kapittel 5</t>
   </si>
@@ -65,19 +65,37 @@
     <t xml:space="preserve">Dette er øvingsmateriell til repetisjons- og øvingsstøtte. I besvarelser, caser, prosjektoppgaver og eksamen gjelder lærebøkene og oppgitte primærkilder.</t>
   </si>
   <si>
+    <t xml:space="preserve">Demografisk</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1A: Ni kriterier på Idas liste: hvilken type, og hvilke er brukbare?</t>
   </si>
   <si>
+    <t xml:space="preserve">Psykografisk</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alene, i par eller i gruppe, slik du vil.</t>
   </si>
   <si>
+    <t xml:space="preserve">Størrelse</t>
+  </si>
+  <si>
     <t xml:space="preserve">Situasjonen</t>
   </si>
   <si>
+    <t xml:space="preserve">Bransje</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ida er kalkulatør hos Nordlys Elektro. Etter tre tapte anbud til borettslag vil hun dele kundene i segmenter, og har skrevet ni kjennetegn hun kan dele etter. Kari spør: hvilke av dem forteller noe om hva kunden trenger, og hvilke er bare lette å måle?</t>
   </si>
   <si>
+    <t xml:space="preserve">Beliggenhet</t>
+  </si>
+  <si>
     <t xml:space="preserve">Begrepene du trenger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viktighet</t>
   </si>
   <si>
     <t xml:space="preserve">Segmenteringskriterium: et kjennetegn ved kjøperne som gir pålitelig indikasjon om felles ønsker og behov. Demografisk: kjennetegn ved mennesker som kan telles (kjønn, alder, sivilstand, utdanning og yrke, inntekt, bosted). Psykografisk: personlighet, livsstil og verdier (Ipsos Norsk Monitor). Bedriftsmarkedet: størrelse, bransje, beliggenhet, viktighet for bedriften.</t>
@@ -157,7 +175,19 @@
     <t xml:space="preserve">Gule celler fyller du inn. Grønne regnes ut av arket. Sjekken til høyre forteller om svaret stemmer, og hva du bør se på hvis ikke.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oppfylt</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1B: Regn segmentet borettslag, og test det mot de fire kravene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ikke oppfylt</t>
   </si>
   <si>
     <t xml:space="preserve">Kari vil sende tilbud til alle 22 borettslagene. Ida vil først vite hvor mye segmentet er verdt, og om det består bokas fire krav til en målgruppe. Hun teller det som kan telles, og antar resten, slik boka sier. Mona i Fjell Elektro gjør det samme for eneboliger bygd før 1980 i Oslo øst.</t>
@@ -274,7 +304,16 @@
     <t xml:space="preserve">Er segmentet borettslag stort nok? Sammenlikn med idrettslagene (600 000 kr), og si hva boka sier om størrelse og lønnsomhet. To–tre setninger. Bruk ordene idrettslag og lønnsom.</t>
   </si>
   <si>
+    <t xml:space="preserve">Udifferensiert</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1C: Kari skal velge Nordlys' målgrupper og strategi. Hva anbefaler du?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Differensiert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konsentrert</t>
   </si>
   <si>
     <t xml:space="preserve">Mandagsmøtet hos Nordlys. Kari vil sende tilbud til alle, Tom vil satse alt på totalentreprenørene, Ida har regnet segmentet borettslag. Nå skal Kari velge: hvem skal Nordlys være best for, hvilken strategi, og hva skjer med resten?</t>
@@ -718,7 +757,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -741,6 +780,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1195,7 +1238,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G42"/>
+  <dimension ref="B1:Z66"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1203,349 +1246,610 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="Z4" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="Z5" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="Z6" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="Z7" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-    </row>
-    <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="Z9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="Z10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z11" s="0" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
+      <c r="B12" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="Z12" s="6" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
+      <c r="B13" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="Z13" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z14" s="0" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
+      <c r="B15" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="Z15" s="6" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="11"/>
-      <c r="G16" s="12" t="str">
+      <c r="B16" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="12"/>
+      <c r="G16" s="13" t="str">
         <f aca="false">IF(C16="","Velg i nedtrekksmenyen.",IF(C16="Demografisk","Riktig. Boligen hører til bosted, et av bokas seks demografiske kriterier. Byggeåret kan telles, og et hus fra før 1980 har ofte et sikringsskap som må byttes.","Ikke riktig. Boligen hører til bosted, et av bokas seks demografiske kriterier. Byggeåret kan telles, og et hus fra før 1980 har ofte et sikringsskap som må byttes."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z16" s="6" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="11"/>
-      <c r="G17" s="12" t="str">
+      <c r="B17" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="12"/>
+      <c r="G17" s="13" t="str">
         <f aca="false">IF(C17="","Velg i nedtrekksmenyen.",IF(C17="Demografisk","Riktig. Inntekt er et demografisk kriterium (5.4). Boka: høy inntekt gir lettere dekning av statusbehov og et annet tilbud.","Ikke riktig. Inntekt er et demografisk kriterium (5.4). Boka: høy inntekt gir lettere dekning av statusbehov og et annet tilbud."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z17" s="6" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="11"/>
-      <c r="G18" s="12" t="str">
+      <c r="B18" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="G18" s="13" t="str">
         <f aca="false">IF(C18="","Velg i nedtrekksmenyen.",IF(C18="Psykografisk","Riktig. Et ønske om bekvemmelighet er en verdi og en livsstil, altså psykografisk (5.5). Vanskelig å fastslå hvem som har det, og hvor sterkt.","Ikke riktig. Et ønske om bekvemmelighet er en verdi og en livsstil, altså psykografisk (5.5). Vanskelig å fastslå hvem som har det, og hvor sterkt."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z18" s="6" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="11"/>
-      <c r="G19" s="12" t="str">
+      <c r="B19" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="G19" s="13" t="str">
         <f aca="false">IF(C19="","Velg i nedtrekksmenyen.",IF(C19="Størrelse","Riktig. Størrelse er det første av bokas fire kriterier på bedriftsmarkedet (5.6). Ulik størrelse gir ulik kalkyle og bemanning.","Ikke riktig. Størrelse er det første av bokas fire kriterier på bedriftsmarkedet (5.6). Ulik størrelse gir ulik kalkyle og bemanning."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z19" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="11"/>
-      <c r="G20" s="12" t="str">
+      <c r="B20" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="12"/>
+      <c r="G20" s="13" t="str">
         <f aca="false">IF(C20="","Velg i nedtrekksmenyen.",IF(C20="Bransje","Riktig. Boka deler bedriftsmarkedet etter bransje: offentlige etater og institusjoner, private bedrifter, organisasjoner (5.6).","Ikke riktig. Boka deler bedriftsmarkedet etter bransje: offentlige etater og institusjoner, private bedrifter, organisasjoner (5.6)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z20" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="11"/>
-      <c r="G21" s="12" t="str">
+      <c r="B21" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="12"/>
+      <c r="G21" s="13" t="str">
         <f aca="false">IF(C21="","Velg i nedtrekksmenyen.",IF(C21="Beliggenhet","Riktig. Beliggenhet avgjør om Nordlys kan love to timers responstid (5.6).","Ikke riktig. Beliggenhet avgjør om Nordlys kan love to timers responstid (5.6)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z21" s="6" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="11"/>
-      <c r="G22" s="12" t="str">
+      <c r="B22" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="12"/>
+      <c r="G22" s="13" t="str">
         <f aca="false">IF(C22="","Velg i nedtrekksmenyen.",IF(C22="Demografisk","Riktig. Alder er et demografisk kriterium (5.4). Enkelt å bruke, og kan telles i statistikken.","Ikke riktig. Alder er et demografisk kriterium (5.4). Enkelt å bruke, og kan telles i statistikken."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z22" s="6" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="11"/>
-      <c r="G23" s="12" t="str">
+      <c r="B23" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="G23" s="13" t="str">
         <f aca="false">IF(C23="","Velg i nedtrekksmenyen.",IF(C23="Viktighet","Riktig. Viktighet for bedriften er det fjerde kriteriet på bedriftsmarkedet (5.6). Byggherrene er 47 % av salgsinntekten.","Ikke riktig. Viktighet for bedriften er det fjerde kriteriet på bedriftsmarkedet (5.6). Byggherrene er 47 % av salgsinntekten."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z23" s="6" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="11"/>
-      <c r="G24" s="12" t="str">
+      <c r="B24" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="12"/>
+      <c r="G24" s="13" t="str">
         <f aca="false">IF(C24="","Velg i nedtrekksmenyen.",IF(C24="Psykografisk","Riktig. Tradisjonell mot moderne er en av de fire livsstilsaksene i Ipsos Norsk Monitor, altså psykografisk (5.5).","Ikke riktig. Tradisjonell mot moderne er en av de fire livsstilsaksene i Ipsos Norsk Monitor, altså psykografisk (5.5)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z24" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z25" s="0" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
+      <c r="B26" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="Z26" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" s="11"/>
-      <c r="G27" s="12" t="str">
+      <c r="B27" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="12"/>
+      <c r="G27" s="13" t="str">
         <f aca="false">IF(C27="","Velg i nedtrekksmenyen.",IF(C27="Ja","Riktig. Et hus fra før 1980 har ofte et sikringsskap som må byttes. Det er et behov, og byggeåret kan telles.","Ikke riktig. Et hus fra før 1980 har ofte et sikringsskap som må byttes. Det er et behov, og byggeåret kan telles."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z27" s="6" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="11"/>
-      <c r="G28" s="12" t="str">
+      <c r="B28" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="12"/>
+      <c r="G28" s="13" t="str">
         <f aca="false">IF(C28="","Velg i nedtrekksmenyen.",IF(C28="Nei","Riktig. Lett å måle, men behovet for en elektriker er det samme. Bokas krav er at kriteriet skiller behov, ikke bare personer.","Ikke riktig. Lett å måle, men behovet for en elektriker er det samme. Bokas krav er at kriteriet skiller behov, ikke bare personer."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z28" s="6" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" s="11"/>
-      <c r="G29" s="12" t="str">
+      <c r="B29" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="12"/>
+      <c r="G29" s="13" t="str">
         <f aca="false">IF(C29="","Velg i nedtrekksmenyen.",IF(C29="Ja","Riktig. Den som har elbil og egen plass, trenger et ladepunkt. Kan telles i statistikken over elbiler.","Ikke riktig. Den som har elbil og egen plass, trenger et ladepunkt. Kan telles i statistikken over elbiler."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z29" s="6" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="11"/>
-      <c r="G30" s="12" t="str">
+      <c r="B30" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="G30" s="13" t="str">
         <f aca="false">IF(C30="","Velg i nedtrekksmenyen.",IF(C30="Nei","Riktig. Innenfor nedslagsfeltet skiller postnummeret adresser, ikke behov. Beliggenhet teller først når avstanden blir så stor at Nordlys ikke er et naturlig valg.","Ikke riktig. Innenfor nedslagsfeltet skiller postnummeret adresser, ikke behov. Beliggenhet teller først når avstanden blir så stor at Nordlys ikke er et naturlig valg."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z30" s="6" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" s="11"/>
-      <c r="G31" s="12" t="str">
+      <c r="B31" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="12"/>
+      <c r="G31" s="13" t="str">
         <f aca="false">IF(C31="","Velg i nedtrekksmenyen.",IF(C31="Ja","Riktig. Boligtypen avgjør hvem som bestemmer: huseieren selv, eller et styre i borettslaget. Det gir ulikt behov og ulikt tilbud.","Ikke riktig. Boligtypen avgjør hvem som bestemmer: huseieren selv, eller et styre i borettslaget. Det gir ulikt behov og ulikt tilbud."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z31" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="11"/>
-      <c r="G32" s="12" t="str">
+      <c r="B32" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="12"/>
+      <c r="G32" s="13" t="str">
         <f aca="false">IF(C32="","Velg i nedtrekksmenyen.",IF(C32="Nei","Riktig. Gift eller enslig: sikringsskapet er det samme. Sivilstand er demografisk, men skiller ikke behovet her.","Ikke riktig. Gift eller enslig: sikringsskapet er det samme. Sivilstand er demografisk, men skiller ikke behovet her."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z32" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z33" s="0" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
+      <c r="B34" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="Z34" s="6" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="Z35" s="6" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="Z36" s="6" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="Z37" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="14" t="str">
+      <c r="B38" s="15" t="str">
         <f aca="false">IF(LEN(B35)&lt;40,"",IF(AND(ISNUMBER(SEARCH("psykograf",B35)),ISNUMBER(SEARCH("demograf",B35))),"Bra: du sier at «miljøbevisst» er psykografisk og vanskelig å fastslå og telle, og at Ida må kombinere med et demografisk kriterium som kan telles, for eksempel eneboliger med egnet tak.",IF(OR(ISNUMBER(SEARCH("psykograf",B35)),ISNUMBER(SEARCH("demograf",B35))),"Du er på sporet. Si både hva slags kriterium «miljøbevisst» er (psykografisk, vanskelig å fastslå), og hva slags kriterium hun bør legge til (demografisk, som kan telles).","Tips: boka sier psykografiske trekk er vanskelige å fastslå, både hvem som har dem og hvor sterkt (5.5). Ida kan verken telle eller finne kundene. Kombiner med noe demografisk som kan telles, som eneboliger med egnet tak, og bruk livsstilen til argumentene i samtalen.")))</f>
         <v/>
       </c>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="Z38" s="6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" s="11"/>
+      <c r="B39" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39" s="12"/>
+      <c r="Z39" s="6" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="16" t="str">
+      <c r="B40" s="17" t="str">
         <f aca="false">IF(C39="JA","Hint: Spør for hvert kjennetegn: kan det telles i statistikken (demografisk eller bedriftsmarkedets fire), eller handler det om personlighet og verdier (psykografisk)? Og: får Nordlys et annet oppdrag fordi kjennetegnet er annerledes? Hvis ikke, skiller det ikke behov.","")</f>
         <v/>
       </c>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="Z40" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z41" s="0" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
+      <c r="B42" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="Z42" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z43" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z44" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z45" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z46" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z47" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z48" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z49" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z50" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z51" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z52" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z53" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z54" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z55" s="0" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z56" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z57" s="0" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z58" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z59" s="0" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z60" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z61" s="0" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z62" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z63" s="0" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z64" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z65" s="0" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z66" s="0" t="s">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -1689,63 +1993,63 @@
   </conditionalFormatting>
   <dataValidations count="16">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C16" type="list">
-      <formula1>"Demografisk,Psykografisk,Størrelse,Bransje,Beliggenhet,Viktighet"</formula1>
+      <formula1>$Z$1:$Z$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C17" type="list">
-      <formula1>"Demografisk,Psykografisk,Størrelse,Bransje,Beliggenhet,Viktighet"</formula1>
+      <formula1>$Z$7:$Z$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C18" type="list">
-      <formula1>"Demografisk,Psykografisk,Størrelse,Bransje,Beliggenhet,Viktighet"</formula1>
+      <formula1>$Z$13:$Z$18</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C19" type="list">
-      <formula1>"Demografisk,Psykografisk,Størrelse,Bransje,Beliggenhet,Viktighet"</formula1>
+      <formula1>$Z$19:$Z$24</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C20" type="list">
-      <formula1>"Demografisk,Psykografisk,Størrelse,Bransje,Beliggenhet,Viktighet"</formula1>
+      <formula1>$Z$25:$Z$30</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C21" type="list">
-      <formula1>"Demografisk,Psykografisk,Størrelse,Bransje,Beliggenhet,Viktighet"</formula1>
+      <formula1>$Z$31:$Z$36</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C22" type="list">
-      <formula1>"Demografisk,Psykografisk,Størrelse,Bransje,Beliggenhet,Viktighet"</formula1>
+      <formula1>$Z$37:$Z$42</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C23" type="list">
-      <formula1>"Demografisk,Psykografisk,Størrelse,Bransje,Beliggenhet,Viktighet"</formula1>
+      <formula1>$Z$43:$Z$48</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C24" type="list">
-      <formula1>"Demografisk,Psykografisk,Størrelse,Bransje,Beliggenhet,Viktighet"</formula1>
+      <formula1>$Z$49:$Z$54</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C27" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$55:$Z$56</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C28" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$57:$Z$58</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C29" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$59:$Z$60</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C30" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$61:$Z$62</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C31" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$63:$Z$64</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C32" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$65:$Z$66</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C39" type="list">
@@ -1768,7 +2072,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G54"/>
+  <dimension ref="B1:Z54"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1776,455 +2080,508 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>51</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="Z4" s="6" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="Z5" s="6" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="B6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="Z6" s="6" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="B7" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="Z7" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="B9" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="Z9" s="6" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="Z10" s="6" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>49</v>
+      <c r="B11" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z11" s="6" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="20" t="n">
+      <c r="B12" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="21" t="n">
         <v>22</v>
       </c>
+      <c r="Z12" s="6" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="21" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z13" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="20" t="n">
-        <v>60</v>
-      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="20" t="n">
+      <c r="B14" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="21" t="n">
         <v>40</v>
       </c>
+      <c r="Z14" s="6" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="21" t="n">
+        <v>12000</v>
+      </c>
+      <c r="Z15" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z16" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="20" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" s="20" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="20" t="n">
+      <c r="B17" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="21" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="20" t="n">
+      <c r="B18" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="21" t="n">
         <v>22400000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="20" t="n">
+      <c r="B19" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="21" t="n">
         <v>14400</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
+      <c r="B21" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
+      <c r="B22" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="G24" s="12" t="str">
+      <c r="B24" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="22"/>
+      <c r="D24" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" s="13" t="str">
         <f aca="false">IF(C24="","Skriv svaret i den gule cellen.",IF(C24=(22*60),"Riktig.",IF(ABS(C24-(22))&lt;=0,"Du har svart antall borettslag. Gang med 60 plasser per borettslag.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="G25" s="12" t="str">
+      <c r="B25" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="22"/>
+      <c r="D25" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="G25" s="13" t="str">
         <f aca="false">IF(C25="","Skriv svaret i den gule cellen.",IF(C25=(22*60*0.4),"Riktig.",IF(ABS(C25-(22*60*0.6))&lt;=0,"Du har tatt de 60 % som allerede har ladepunkt. Segmentet er de 40 % som mangler.",IF(ABS(C25-(22*60))&lt;=0,"Du har svart alle plassene. Bare 40 % av dem mangler ladepunkt.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C26" s="21"/>
-      <c r="D26" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="G26" s="12" t="str">
+      <c r="B26" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="22"/>
+      <c r="D26" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="G26" s="13" t="str">
         <f aca="false">IF(C26="","Skriv svaret i den gule cellen.",IF(C26=(22*60*0.4*12000),"Riktig.",IF(ABS(C26-(22*60*12000))&lt;=0,"Du har ganget alle plassene med prisen. Bare de 528 som mangler ladepunkt, er et salg.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" s="21"/>
-      <c r="D27" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="G27" s="12" t="str">
+      <c r="B27" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="22"/>
+      <c r="D27" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" s="13" t="str">
         <f aca="false">IF(C27="","Skriv svaret i den gule cellen.",IF(C27=(22*60*0.4*12000/4),"Riktig.",IF(ABS(C27-(22*60*0.4*12000))&lt;=0,"Det er hele salgsverdien. Styrene bygger ut over fire år; del på 4.",IF(ABS(C27-(22*60*0.4*12000*4))&lt;=0,"Du har ganget med 4. Salgsverdien skal deles på årene, ikke ganges.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28" s="23"/>
-      <c r="D28" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="G28" s="12" t="str">
+      <c r="B28" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="24"/>
+      <c r="D28" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="G28" s="13" t="str">
         <f aca="false">IF(C28="","Skriv svaret i den gule cellen.",IF(ABS(C28-(ROUND(22*60*0.4*12000/4/22400000*100,0)))&lt;=0.5,"Riktig.",IF(ABS(C28-(ROUND(22*60*0.4*12000/22400000*100,0)))&lt;=0.5,"Du har regnet andelen av hele salgsverdien, 6 336 000. Bruk tallet per år, 1 584 000.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C29" s="21"/>
-      <c r="D29" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="G29" s="12" t="str">
+      <c r="B29" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="22"/>
+      <c r="D29" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G29" s="13" t="str">
         <f aca="false">IF(C29="","Skriv svaret i den gule cellen.",IF(C29=(22*60*0.4*2/4),"Riktig.",IF(ABS(C29-(22*60*0.4*2))&lt;=0,"Det er timene for alle fire årene. Del på 4.",IF(ABS(C29-(22*60*0.4/4))&lt;=0,"Du har glemt at hvert ladepunkt tar 2 timer.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" s="21"/>
-      <c r="D31" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="G31" s="12" t="str">
+      <c r="B31" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="G31" s="13" t="str">
         <f aca="false">IF(C31="","Skriv svaret i den gule cellen.",IF(C31=(4000*0.45*0.05),"Riktig.",IF(ABS(C31-(4000*0.45))&lt;=0,"Det er antall eneboliger bygd før 1980, 1 800. Bare 5 % av dem bytter skap i året.",IF(ABS(C31-(4000*0.05))&lt;=0,"Du har glemt at bare 45 % av eneboligene er bygd før 1980.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" s="24"/>
-      <c r="D32" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="G32" s="12" t="str">
+      <c r="B32" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="25"/>
+      <c r="D32" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="G32" s="13" t="str">
         <f aca="false">IF(C32="","Skriv svaret i den gule cellen.",IF(ABS(C32-(ROUND(4000*0.45*0.05*6/3500*100,1)))&lt;=0.05,"Riktig.",IF(ABS(C32-(ROUND(4000*0.45*0.05/3500*100,1)))&lt;=0.05,"Du har delt bytter på timer. Hvert bytte tar 6 timer; gang først med 6.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
+      <c r="B34" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C35" s="11"/>
-      <c r="G35" s="12" t="str">
+      <c r="B35" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="12"/>
+      <c r="G35" s="13" t="str">
         <f aca="false">IF(C35="","Velg i nedtrekksmenyen.",IF(C35="Oppfylt","Riktig. 22 borettslag er telt, plassene og andelen uten lader er rimelige antagelser. Det er slik boka sier segmentet skal måles (5.7).","Ikke riktig. 22 borettslag er telt, plassene og andelen uten lader er rimelige antagelser. Det er slik boka sier segmentet skal måles (5.7)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C36" s="11"/>
-      <c r="G36" s="12" t="str">
+      <c r="B36" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" s="12"/>
+      <c r="G36" s="13" t="str">
         <f aca="false">IF(C36="","Velg i nedtrekksmenyen.",IF(C36="Oppfylt","Riktig. Alle 22 ligger innenfor kjøreavstand, og styrene kan kontaktes direkte, ett og ett.","Ikke riktig. Alle 22 ligger innenfor kjøreavstand, og styrene kan kontaktes direkte, ett og ett."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C37" s="11"/>
-      <c r="G37" s="12" t="str">
+      <c r="B37" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" s="12"/>
+      <c r="G37" s="13" t="str">
         <f aca="false">IF(C37="","Velg i nedtrekksmenyen.",IF(C37="Oppfylt","Riktig. 1 584 000 kr i året er mer enn idrettslagene (600 000) og mer enn husstandene (1 450 000). Over et rimelig minstemål.","Ikke riktig. 1 584 000 kr i året er mer enn idrettslagene (600 000) og mer enn husstandene (1 450 000). Over et rimelig minstemål."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C38" s="11"/>
-      <c r="G38" s="12" t="str">
+      <c r="B38" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" s="12"/>
+      <c r="G38" s="13" t="str">
         <f aca="false">IF(C38="","Velg i nedtrekksmenyen.",IF(C38="Oppfylt","Riktig. 264 timer i året er 1,8 % av 14 400. Nordlys har teknikken og folkene, og kan bygge trinnvis.","Ikke riktig. 264 timer i året er 1,8 % av 14 400. Nordlys har teknikken og folkene, og kan bygge trinnvis."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
+      <c r="B40" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C41" s="11"/>
-      <c r="G41" s="12" t="str">
+      <c r="B41" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C41" s="12"/>
+      <c r="G41" s="13" t="str">
         <f aca="false">IF(C41="","Velg i nedtrekksmenyen.",IF(C41="Oppfylt","Riktig. Statistikken teller elbiler per kommune. Segmentet kan beskrives og måles.","Ikke riktig. Statistikken teller elbiler per kommune. Segmentet kan beskrives og måles."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C42" s="11"/>
-      <c r="G42" s="12" t="str">
+      <c r="B42" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" s="12"/>
+      <c r="G42" s="13" t="str">
         <f aca="false">IF(C42="","Velg i nedtrekksmenyen.",IF(C42="Ikke oppfylt","Riktig. 12 montører på ett sted når ikke hele Oslo med responstid, og ingen kanal når bare dem. Boka: beliggenheten må gjøre bedriften til et naturlig valg.","Ikke riktig. 12 montører på ett sted når ikke hele Oslo med responstid, og ingen kanal når bare dem. Boka: beliggenheten må gjøre bedriften til et naturlig valg."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C43" s="11"/>
-      <c r="G43" s="12" t="str">
+      <c r="B43" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="12"/>
+      <c r="G43" s="13" t="str">
         <f aca="false">IF(C43="","Velg i nedtrekksmenyen.",IF(C43="Oppfylt","Riktig. Segmentet er så stort at ingen tviler på salgsverdien. Men boka minner om at der er konkurransen størst og prisene under press.","Ikke riktig. Segmentet er så stort at ingen tviler på salgsverdien. Men boka minner om at der er konkurransen størst og prisene under press."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="C44" s="11"/>
-      <c r="G44" s="12" t="str">
+      <c r="B44" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" s="12"/>
+      <c r="G44" s="13" t="str">
         <f aca="false">IF(C44="","Velg i nedtrekksmenyen.",IF(C44="Ikke oppfylt","Riktig. 14 400 timer er brukt opp. Nordlys kan ikke levere mengden til rett tid til hele Oslo. Avgrens segmentet i stedet.","Ikke riktig. 14 400 timer er brukt opp. Nordlys kan ikke levere mengden til rett tid til hele Oslo. Avgrens segmentet i stedet."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
+      <c r="B46" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
+      <c r="B49" s="14"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
     </row>
     <row r="50" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="14" t="str">
+      <c r="B50" s="15" t="str">
         <f aca="false">IF(LEN(B47)&lt;40,"",IF(AND(ISNUMBER(SEARCH("idrettslag",B47)),ISNUMBER(SEARCH("lønnsom",B47))),"Bra: du sammenlikner med idrettslagene og har med bokas poeng om at det største segmentet ikke alltid er det mest lønnsomme.",IF(OR(ISNUMBER(SEARCH("idrettslag",B47)),ISNUMBER(SEARCH("lønnsom",B47))),"Du er på sporet. Ta med både sammenlikningen med idrettslagene (600 000 kr) og det boka sier om at det største segmentet ikke alltid er det mest lønnsomme.","Tips: 1 584 000 kr i året er mer enn idrettslagene med 600 000 og mer enn husstandene med 1 450 000, så det er over et rimelig minstemål. Og boka: det største segmentet, byggherrene, er ikke alltid det mest lønnsomme, for der er konkurransen størst og prisene under press.")))</f>
         <v/>
       </c>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="15"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="C51" s="11"/>
+      <c r="B51" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C51" s="12"/>
     </row>
     <row r="52" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="16" t="str">
+      <c r="B52" s="17" t="str">
         <f aca="false">IF(C51="JA","Hint: a: 22 × 60 = 1 320. b: 1 320 × 0,40 = 528. c: 528 × 12 000 = 6 336 000. d: 6 336 000 / 4 = 1 584 000. e: 1 584 000 / 22 400 000 = 7,07 %, avrundet 7. f: 528 × 2 / 4 = 264. g: 4 000 × 0,45 × 0,05 = 90. h: 90 × 6 = 540 timer, 540 / 3 500 = 15,4 %.","")</f>
         <v/>
       </c>
-      <c r="C52" s="16"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="17"/>
     </row>
     <row r="54" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
+      <c r="B54" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -2376,35 +2733,35 @@
   </conditionalFormatting>
   <dataValidations count="9">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C35" type="list">
-      <formula1>"Oppfylt,Ikke oppfylt"</formula1>
+      <formula1>$Z$1:$Z$2</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C36" type="list">
-      <formula1>"Oppfylt,Ikke oppfylt"</formula1>
+      <formula1>$Z$3:$Z$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C37" type="list">
-      <formula1>"Oppfylt,Ikke oppfylt"</formula1>
+      <formula1>$Z$5:$Z$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C38" type="list">
-      <formula1>"Oppfylt,Ikke oppfylt"</formula1>
+      <formula1>$Z$7:$Z$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C41" type="list">
-      <formula1>"Oppfylt,Ikke oppfylt"</formula1>
+      <formula1>$Z$9:$Z$10</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C42" type="list">
-      <formula1>"Oppfylt,Ikke oppfylt"</formula1>
+      <formula1>$Z$11:$Z$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C43" type="list">
-      <formula1>"Oppfylt,Ikke oppfylt"</formula1>
+      <formula1>$Z$13:$Z$14</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C44" type="list">
-      <formula1>"Oppfylt,Ikke oppfylt"</formula1>
+      <formula1>$Z$15:$Z$16</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C51" type="list">
@@ -2427,7 +2784,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G52"/>
+  <dimension ref="B1:Z52"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2435,460 +2792,564 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>91</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="6" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="Z3" s="6" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="Z4" s="6" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="Z5" s="6" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="Z6" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="Z7" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="Z9" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="Z10" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z11" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" s="21" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="Z12" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="21" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z13" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="21" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Z14" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="21" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="Z15" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="21" t="n">
+        <v>1450000</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="Z16" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" s="20" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="D12" s="25" t="n">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="C13" s="20" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="D13" s="25" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" s="20" t="n">
-        <v>3800000</v>
-      </c>
-      <c r="D14" s="25" t="n">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="C15" s="20" t="n">
-        <v>1650000</v>
-      </c>
-      <c r="D15" s="25" t="n">
-        <v>0.07</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" s="20" t="n">
-        <v>1450000</v>
-      </c>
-      <c r="D16" s="25" t="n">
-        <v>0.06</v>
-      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="C17" s="20" t="n">
+      <c r="B17" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="21" t="n">
         <v>600000</v>
       </c>
-      <c r="D17" s="25" t="n">
+      <c r="D17" s="26" t="n">
         <v>0.03</v>
       </c>
+      <c r="Z17" s="6" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="C18" s="20" t="n">
+      <c r="B18" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="21" t="n">
         <v>22400000</v>
       </c>
-      <c r="D18" s="25" t="n">
+      <c r="D18" s="26" t="n">
         <v>1</v>
       </c>
+      <c r="Z18" s="6" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="C19" s="20" t="n">
+      <c r="B19" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C19" s="21" t="n">
         <v>1584000</v>
       </c>
-      <c r="D19" s="25" t="s">
-        <v>97</v>
+      <c r="D19" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z19" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z20" s="0" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="Z21" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="Z22" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z23" s="0" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
+      <c r="B24" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="Z24" s="6" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="C25" s="11"/>
-      <c r="G25" s="12" t="str">
+      <c r="B25" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="G25" s="13" t="str">
         <f aca="false">IF(C25="","Velg i nedtrekksmenyen.",IF(C25="Udifferensiert","Riktig. Samme tilbud til alle kunder og kundegrupper. Boka: utnytter ikke mulighetene segmenteringen gir (5.8.1).","Ikke riktig. Samme tilbud til alle kunder og kundegrupper. Boka: utnytter ikke mulighetene segmenteringen gir (5.8.1)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z25" s="6" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="C26" s="11"/>
-      <c r="G26" s="12" t="str">
+      <c r="B26" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26" s="12"/>
+      <c r="G26" s="13" t="str">
         <f aca="false">IF(C26="","Velg i nedtrekksmenyen.",IF(C26="Differensiert","Riktig. Forskjellige tilbud til forskjellige kundegrupper, knyttet til service, produkt og kommunikasjon (5.8.2). Det koster å holde tre tilbud.","Ikke riktig. Forskjellige tilbud til forskjellige kundegrupper, knyttet til service, produkt og kommunikasjon (5.8.2). Det koster å holde tre tilbud."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z26" s="6" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C27" s="11"/>
-      <c r="G27" s="12" t="str">
+      <c r="B27" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C27" s="12"/>
+      <c r="G27" s="13" t="str">
         <f aca="false">IF(C27="","Velg i nedtrekksmenyen.",IF(C27="Konsentrert","Riktig. Markedet er segmentert, men bedriften konsentrerer seg om ett segment. Liten markedsandel, men lønnsomheten kan være betydelig (5.8.3).","Ikke riktig. Markedet er segmentert, men bedriften konsentrerer seg om ett segment. Liten markedsandel, men lønnsomheten kan være betydelig (5.8.3)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z27" s="6" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C28" s="11"/>
-      <c r="G28" s="12" t="str">
+      <c r="B28" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C28" s="12"/>
+      <c r="G28" s="13" t="str">
         <f aca="false">IF(C28="","Velg i nedtrekksmenyen.",IF(C28="Konsentrert","Riktig. Ett segment, alt på det. Det er konsentrert, selv om segmentet er stort. Boka advarer: i store segmenter er konkurransen størst.","Ikke riktig. Ett segment, alt på det. Det er konsentrert, selv om segmentet er stort. Boka advarer: i store segmenter er konkurransen størst."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z28" s="6" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="C29" s="11"/>
-      <c r="G29" s="12" t="str">
+      <c r="B29" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C29" s="12"/>
+      <c r="G29" s="13" t="str">
         <f aca="false">IF(C29="","Velg i nedtrekksmenyen.",IF(C29="Udifferensiert","Riktig. Samme kommunikasjon til alle. Boka: kan være et bevisst valg, eller skyldes mangelfull markedskunnskap (5.8.1).","Ikke riktig. Samme kommunikasjon til alle. Boka: kan være et bevisst valg, eller skyldes mangelfull markedskunnskap (5.8.1)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z29" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z30" s="0" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
+      <c r="B31" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="Z31" s="6" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="C32" s="11"/>
-      <c r="G32" s="12" t="str">
+      <c r="B32" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C32" s="12"/>
+      <c r="G32" s="13" t="str">
         <f aca="false">IF(C32="","Velg i nedtrekksmenyen.",IF(C32="Størrelse","Riktig. Størrelsen på prosjektet avgjør kalkyle og bemanning (5.6).","Ikke riktig. Størrelsen på prosjektet avgjør kalkyle og bemanning (5.6)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="C33" s="11"/>
-      <c r="G33" s="12" t="str">
+      <c r="B33" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C33" s="12"/>
+      <c r="G33" s="13" t="str">
         <f aca="false">IF(C33="","Velg i nedtrekksmenyen.",IF(C33="Bransje","Riktig. Boka deler i offentlige etater, private bedrifter og organisasjoner. Kommunen kjøper på anbud med krav til dokumentasjon og lærlingtimer (5.6).","Ikke riktig. Boka deler i offentlige etater, private bedrifter og organisasjoner. Kommunen kjøper på anbud med krav til dokumentasjon og lærlingtimer (5.6)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="C34" s="11"/>
-      <c r="G34" s="12" t="str">
+      <c r="B34" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C34" s="12"/>
+      <c r="G34" s="13" t="str">
         <f aca="false">IF(C34="","Velg i nedtrekksmenyen.",IF(C34="Beliggenhet","Riktig. Beliggenheten avgjør hva Nordlys kan love. Lenger unna: planlagte oppdrag (5.6).","Ikke riktig. Beliggenheten avgjør hva Nordlys kan love. Lenger unna: planlagte oppdrag (5.6)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="C35" s="11"/>
-      <c r="G35" s="12" t="str">
+      <c r="B35" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" s="12"/>
+      <c r="G35" s="13" t="str">
         <f aca="false">IF(C35="","Velg i nedtrekksmenyen.",IF(C35="Viktighet","Riktig. Viktighet for bedriften: hvem som får de beste folkene når det er knapt, bør være bestemt på forhånd (5.6).","Ikke riktig. Viktighet for bedriften: hvem som får de beste folkene når det er knapt, bør være bestemt på forhånd (5.6)."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
+      <c r="B37" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
+      <c r="B38" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
     </row>
     <row r="39" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="C39" s="24"/>
-      <c r="D39" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="G39" s="12" t="str">
+      <c r="B39" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C39" s="25"/>
+      <c r="D39" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="G39" s="13" t="str">
         <f aca="false">IF(C39="","Skriv svaret i den gule cellen.",IF(ABS(C39-(ROUND(1584000/288000,1)))&lt;=0.05,"Riktig.",IF(ABS(C39-(22))&lt;=0.05,"Du har svart alle 22 borettslagene. De bygger ut over fire år; 1 584 000 kr i året er 5,5 anlegg.",IF(ABS(C39-(ROUND(6336000/288000,1)))&lt;=0.05,"Du har delt hele salgsverdien, 6 336 000, på ett anlegg. Det er 22 anlegg over fire år. Per år: 1 584 000 / 288 000.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C40" s="21"/>
-      <c r="D40" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="G40" s="12" t="str">
+      <c r="B40" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C40" s="22"/>
+      <c r="D40" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="G40" s="13" t="str">
         <f aca="false">IF(C40="","Skriv svaret i den gule cellen.",IF(ABS(C40-(ROUND(1584000/288000*48,0)))&lt;=1,"Riktig.",IF(ABS(C40-(48))&lt;=1,"Det er timene for ett anlegg. Gang med 5,5 anlegg i året.",IF(ABS(C40-(22*48))&lt;=1,"Du har tatt alle 22 anleggene. Det er over fire år; per år er det 5,5 anlegg.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C41" s="21"/>
-      <c r="D41" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="G41" s="12" t="str">
+      <c r="B41" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C41" s="22"/>
+      <c r="D41" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="G41" s="13" t="str">
         <f aca="false">IF(C41="","Skriv svaret i den gule cellen.",IF(C41=(22400000+1584000),"Riktig.",IF(ABS(C41-(22400000+6336000))&lt;=0,"Du har lagt til hele salgsverdien over fire år. Per år er det 1 584 000.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C42" s="24"/>
-      <c r="D42" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="G42" s="12" t="str">
+      <c r="B42" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C42" s="25"/>
+      <c r="D42" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="G42" s="13" t="str">
         <f aca="false">IF(C42="","Skriv svaret i den gule cellen.",IF(ABS(C42-(ROUND(1584000/(22400000+1584000)*100,1)))&lt;=0.05,"Riktig.",IF(ABS(C42-(ROUND(1584000/22400000*100,1)))&lt;=0.05,"Du har delt på den gamle salgsinntekten, 22 400 000. Borettslagene kommer i tillegg; del på 23 984 000.",IF(ABS(C42-(ROUND(6336000/(22400000+1584000)*100,1)))&lt;=0.05,"Du har brukt hele salgsverdien, 6 336 000. Bruk tallet per år, 1 584 000.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
+      <c r="B44" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
     </row>
     <row r="48" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="14" t="str">
+      <c r="B48" s="15" t="str">
         <f aca="false">IF(LEN(B45)&lt;40,"",IF(AND(ISNUMBER(SEARCH("ifferensiert",B45)),ISNUMBER(SEARCH("krav",B45))),"Bra: du navngir strategien, tester mot kravene og sier hva som skjer med resten. Sjekk at du også har med et tall (1 584 000 kr, 264 timer eller 47 %).",IF(OR(ISNUMBER(SEARCH("ifferensiert",B45)),ISNUMBER(SEARCH("krav",B45))),"Du er på sporet. Navngi strategien (differensiert eller konsentrert), og vis at du har testet målgruppene mot de fire kravene.","Tips: et godt svar velger for eksempel borettslagene (1 584 000 kr, 264 timer, består alle fire krav) og næringskundene (responstid), kaller strategien differensiert, og sier at byggherrene beholdes med færre og større jobber mens husstander og idrettslag tas når de kommer.")))</f>
         <v/>
       </c>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="15"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="C49" s="11"/>
+      <c r="B49" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C49" s="12"/>
     </row>
     <row r="50" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="16" t="str">
+      <c r="B50" s="17" t="str">
         <f aca="false">IF(C49="JA","Hint: a: 1 584 000 / 288 000 = 5,5 anlegg. b: 5,5 × 48 = 264 timer. c: 22 400 000 + 1 584 000 = 23 984 000. d: 1 584 000 / 23 984 000 = 6,6 %. Strategiene: samme tilbud til alle er udifferensiert, ulike tilbud til ulike grupper er differensiert, alt på ett segment er konsentrert.","")</f>
         <v/>
       </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="17"/>
     </row>
     <row r="52" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="6"/>
+      <c r="B52" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -3018,39 +3479,39 @@
   </conditionalFormatting>
   <dataValidations count="10">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C25" type="list">
-      <formula1>"Udifferensiert,Differensiert,Konsentrert"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C26" type="list">
-      <formula1>"Udifferensiert,Differensiert,Konsentrert"</formula1>
+      <formula1>$Z$4:$Z$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C27" type="list">
-      <formula1>"Udifferensiert,Differensiert,Konsentrert"</formula1>
+      <formula1>$Z$7:$Z$9</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C28" type="list">
-      <formula1>"Udifferensiert,Differensiert,Konsentrert"</formula1>
+      <formula1>$Z$10:$Z$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C29" type="list">
-      <formula1>"Udifferensiert,Differensiert,Konsentrert"</formula1>
+      <formula1>$Z$13:$Z$15</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C32" type="list">
-      <formula1>"Størrelse,Bransje,Beliggenhet,Viktighet"</formula1>
+      <formula1>$Z$16:$Z$19</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C33" type="list">
-      <formula1>"Størrelse,Bransje,Beliggenhet,Viktighet"</formula1>
+      <formula1>$Z$20:$Z$23</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C34" type="list">
-      <formula1>"Størrelse,Bransje,Beliggenhet,Viktighet"</formula1>
+      <formula1>$Z$24:$Z$27</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C35" type="list">
-      <formula1>"Størrelse,Bransje,Beliggenhet,Viktighet"</formula1>
+      <formula1>$Z$28:$Z$31</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C49" type="list">
@@ -3083,239 +3544,239 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="26" t="s">
-        <v>119</v>
+      <c r="B2" s="27" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="B3" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>123</v>
+      <c r="B5" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="28" t="s">
-        <v>125</v>
+      <c r="B6" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="30"/>
+      <c r="D6" s="29" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="28" t="s">
-        <v>127</v>
+      <c r="B7" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="30"/>
+      <c r="D7" s="29" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="28" t="s">
-        <v>129</v>
+      <c r="B8" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8" s="30"/>
+      <c r="D8" s="29" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="28" t="s">
-        <v>130</v>
-      </c>
-      <c r="C9" s="29" t="n">
+      <c r="B9" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" s="30" t="n">
         <v>1320</v>
       </c>
-      <c r="D9" s="28" t="s">
-        <v>131</v>
+      <c r="D9" s="29" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="C10" s="29" t="n">
+      <c r="B10" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" s="30" t="n">
         <v>528</v>
       </c>
-      <c r="D10" s="28" t="s">
-        <v>133</v>
+      <c r="D10" s="29" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="C11" s="29" t="n">
+      <c r="B11" s="29" t="s">
+        <v>147</v>
+      </c>
+      <c r="C11" s="30" t="n">
         <v>6336000</v>
       </c>
-      <c r="D11" s="28" t="s">
-        <v>135</v>
+      <c r="D11" s="29" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="28" t="s">
-        <v>136</v>
-      </c>
-      <c r="C12" s="29" t="n">
+      <c r="B12" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" s="30" t="n">
         <v>1584000</v>
       </c>
-      <c r="D12" s="28" t="s">
-        <v>137</v>
+      <c r="D12" s="29" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="C13" s="29" t="n">
+      <c r="B13" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="C13" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="D13" s="28" t="s">
-        <v>139</v>
+      <c r="D13" s="29" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="C14" s="29" t="n">
+      <c r="B14" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="C14" s="30" t="n">
         <v>264</v>
       </c>
-      <c r="D14" s="28" t="s">
-        <v>141</v>
+      <c r="D14" s="29" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="28" t="s">
-        <v>142</v>
-      </c>
-      <c r="C15" s="29" t="n">
+      <c r="B15" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="C15" s="30" t="n">
         <v>90</v>
       </c>
-      <c r="D15" s="28" t="s">
-        <v>143</v>
+      <c r="D15" s="29" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="C16" s="29" t="n">
+      <c r="B16" s="29" t="s">
+        <v>157</v>
+      </c>
+      <c r="C16" s="30" t="n">
         <v>15.4</v>
       </c>
-      <c r="D16" s="28" t="s">
-        <v>145</v>
+      <c r="D16" s="29" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="C17" s="29"/>
-      <c r="D17" s="28" t="s">
-        <v>147</v>
+      <c r="B17" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" s="30"/>
+      <c r="D17" s="29" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="28" t="s">
-        <v>149</v>
+      <c r="B18" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="C18" s="30"/>
+      <c r="D18" s="29" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="28" t="s">
-        <v>150</v>
-      </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="28" t="s">
-        <v>151</v>
+      <c r="B19" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="C19" s="30"/>
+      <c r="D19" s="29" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="C20" s="29"/>
-      <c r="D20" s="28" t="s">
-        <v>153</v>
+      <c r="B20" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="C20" s="30"/>
+      <c r="D20" s="29" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="28" t="s">
-        <v>154</v>
-      </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="28" t="s">
-        <v>155</v>
+      <c r="B21" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="C21" s="30"/>
+      <c r="D21" s="29" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="28" t="s">
-        <v>156</v>
-      </c>
-      <c r="C22" s="29" t="n">
+      <c r="B22" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="C22" s="30" t="n">
         <v>5.5</v>
       </c>
-      <c r="D22" s="28" t="s">
-        <v>157</v>
+      <c r="D22" s="29" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="C23" s="29" t="n">
+      <c r="B23" s="29" t="s">
+        <v>171</v>
+      </c>
+      <c r="C23" s="30" t="n">
         <v>264</v>
       </c>
-      <c r="D23" s="28" t="s">
-        <v>159</v>
+      <c r="D23" s="29" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="C24" s="29" t="n">
+      <c r="B24" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="C24" s="30" t="n">
         <v>23984000</v>
       </c>
-      <c r="D24" s="28" t="s">
-        <v>161</v>
+      <c r="D24" s="29" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="28" t="s">
-        <v>162</v>
-      </c>
-      <c r="C25" s="29" t="n">
+      <c r="B25" s="29" t="s">
+        <v>175</v>
+      </c>
+      <c r="C25" s="30" t="n">
         <v>6.6</v>
       </c>
-      <c r="D25" s="28" t="s">
-        <v>163</v>
+      <c r="D25" s="29" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="28" t="s">
-        <v>164</v>
-      </c>
-      <c r="C26" s="29"/>
-      <c r="D26" s="28" t="s">
-        <v>165</v>
+      <c r="B26" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="C26" s="30"/>
+      <c r="D26" s="29" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/pensum/ma05/MA05_Markedssegmentering_Oppgaver_v6.xlsx
+++ b/pensum/ma05/MA05_Markedssegmentering_Oppgaver_v6.xlsx
@@ -199,7 +199,7 @@
     <t xml:space="preserve">Forutsetningene, slik Ida satte dem opp</t>
   </si>
   <si>
-    <t xml:space="preserve">Boka sier segmentet skal måles med offentlig statistikk supplert med rimelige antagelser (5.7). Tallene under er Idas. Telt: 22 borettslag og sameier med felles parkering i nedslagsfeltet. Antatt: 60 parkeringsplasser i snitt, 40 % av plassene mangler ladepunkt, 12 000 kr per ladepunkt installert (midt i prisguidens 8 000–20 000 kr), fire år før styrene har bygd ut. Et ladepunkt tar 2 montørtimer. Nordlys har 22 400 000 kr i salgsinntekt og 14 400 fakturerbare timer. Fjell Elektro: 4 000 eneboliger i Oslo øst, 45 % bygd før 1980, 5 % av dem bytter sikringsskap i året, 6 timer per bytte, 3 500 fakturerbare timer.</t>
+    <t xml:space="preserve">Boka sier segmentet skal måles med offentlig statistikk supplert med rimelige antagelser (5.7). Tallene under er Idas. Telt: 22 borettslag og sameier med felles parkering i nedslagsfeltet. Antatt: 60 parkeringsplasser i snitt, 40 % av plassene mangler ladepunkt, 20 800 kr per ladepunkt i et felles anlegg (bokser og felles infrastruktur, kapittel 2), fire år før styrene har bygd ut. Et ladepunkt i et felles anlegg tar 8,5 montørtimer (kapittel 2: 51 timer for seks plasser). Nordlys har 22 400 000 kr i salgsinntekt og 14 400 fakturerbare timer. Fjell Elektro: 4 000 eneboliger i Oslo øst, 45 % bygd før 1980, 5 % av dem bytter sikringsskap i året, 14 timer per bytte, 3 500 fakturerbare timer.</t>
   </si>
   <si>
     <t xml:space="preserve">Forutsetning</t>
@@ -217,13 +217,13 @@
     <t xml:space="preserve">Andel av plassene uten ladepunkt (antatt), prosent</t>
   </si>
   <si>
-    <t xml:space="preserve">Pris per ladepunkt installert, kr</t>
+    <t xml:space="preserve">Pris per ladepunkt i felles anlegg, kr (kapittel 2)</t>
   </si>
   <si>
     <t xml:space="preserve">År før styrene har bygd ut (antatt)</t>
   </si>
   <si>
-    <t xml:space="preserve">Montørtimer per ladepunkt (faktaarket)</t>
+    <t xml:space="preserve">Montørtimer per ladepunkt i felles anlegg (kapittel 2)</t>
   </si>
   <si>
     <t xml:space="preserve">Nordlys' salgsinntekt 2026, kr</t>
@@ -250,7 +250,7 @@
     <t xml:space="preserve">ladepunkt</t>
   </si>
   <si>
-    <t xml:space="preserve">c) Salgsverdien i segmentet: ladepunkt × 12 000 kr</t>
+    <t xml:space="preserve">c) Salgsverdien i segmentet: ladepunkt × 20 800 kr</t>
   </si>
   <si>
     <t xml:space="preserve">kr</t>
@@ -268,7 +268,7 @@
     <t xml:space="preserve">prosent</t>
   </si>
   <si>
-    <t xml:space="preserve">f) Montørtimer per år: ladepunkt × 2 timer, delt på 4 år</t>
+    <t xml:space="preserve">f) Montørtimer per år: ladepunkt × 8,5 timer, delt på 4 år</t>
   </si>
   <si>
     <t xml:space="preserve">timer per år</t>
@@ -280,7 +280,7 @@
     <t xml:space="preserve">bytter</t>
   </si>
   <si>
-    <t xml:space="preserve">h) Fjell: andel av 3 500 timer, i prosent med én desimal: bytter × 6 timer / 3 500 × 100</t>
+    <t xml:space="preserve">h) Fjell: andel av 3 500 timer, i prosent med én desimal: bytter × 14 timer / 3 500 × 100</t>
   </si>
   <si>
     <t xml:space="preserve">De fire kravene: borettslag og sameier i nedslagsfeltet uten ladeanlegg (velg Oppfylt eller Ikke oppfylt)</t>
@@ -316,7 +316,7 @@
     <t xml:space="preserve">Konsentrert</t>
   </si>
   <si>
-    <t xml:space="preserve">Mandagsmøtet hos Nordlys. Kari vil sende tilbud til alle, Tom vil satse alt på totalentreprenørene, Ida har regnet segmentet borettslag. Nå skal Kari velge: hvem skal Nordlys være best for, hvilken strategi, og hva skjer med resten?</t>
+    <t xml:space="preserve">Mandagsmøtet hos Nordlys. Kari vil sende tilbud til alle, formann Ronny vil satse alt på totalentreprenørene, Ida har regnet segmentet borettslag. Nå skal Kari velge: hvem skal Nordlys være best for, hvilken strategi, og hva skjer med resten?</t>
   </si>
   <si>
     <t xml:space="preserve">Udifferensiert markedsføring: samme tilbud til alle. Differensiert: forskjellige tilbud til forskjellige kundegrupper. Konsentrert: alt på ett eller noen få segmenter. Bedriftsmarkedets kriterier: størrelse, bransje, beliggenhet, viktighet. Et segment finner du; en målgruppe velger du, etter de fire kravene.</t>
@@ -325,7 +325,7 @@
     <t xml:space="preserve">Nordlys' kundegrupper, slik Ida satte dem opp</t>
   </si>
   <si>
-    <t xml:space="preserve">Salgsinntekten for 2026 er 22 400 000 kr (faktaarket), fordelt på seks kundegrupper. Borettslagene er regnet i oppgave 1B: 1 584 000 kr i året, 528 ladepunkt over fire år. Ett borettslagsanlegg er 528 / 22 = 24 ladepunkt: 24 × 12 000 kr = 288 000 kr og 24 × 2 timer = 48 montørtimer.</t>
+    <t xml:space="preserve">Salgsinntekten for 2026 er 22 400 000 kr (faktaarket), fordelt på seks kundegrupper. Borettslagene er regnet i oppgave 1B: 2 745 600 kr i året, 528 ladepunkt over fire år. Ett borettslagsanlegg er 528 / 22 = 24 ladepunkt: 24 × 20 800 kr = 499 200 kr og 24 × 8,5 timer = 204 montørtimer.</t>
   </si>
   <si>
     <t xml:space="preserve">Kundegruppe</t>
@@ -382,10 +382,10 @@
     <t xml:space="preserve">Mona i Fjell Elektro: «Vi tar bare eneboliger fra før 1980 i Oslo øst.»</t>
   </si>
   <si>
-    <t xml:space="preserve">Tom: «Glem resten. Vi satser alt på totalentreprenørene.»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronny: «Samme brosjyre til huseiere, borettslag og byggherrer sparer tid.»</t>
+    <t xml:space="preserve">Ronny: «Glem resten. Vi satser alt på totalentreprenørene.»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom: «Samme brosjyre til huseiere, borettslag og byggherrer sparer tid.»</t>
   </si>
   <si>
     <t xml:space="preserve">Del 2: Hvilket av bokas fire kriterier på bedriftsmarkedet bruker Nordlys her? (velg i nedtrekksmenyen)</t>
@@ -406,22 +406,22 @@
     <t xml:space="preserve">Del 3: Regn</t>
   </si>
   <si>
-    <t xml:space="preserve">Ett borettslagsanlegg er 24 ladepunkt, 288 000 kr og 48 montørtimer. Segmentet gir 1 584 000 kr i året (1B).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a) Anlegg Nordlys må vinne i året: 1 584 000 / 288 000, én desimal</t>
+    <t xml:space="preserve">Ett borettslagsanlegg er 24 ladepunkt, 499 200 kr og 204 montørtimer. Segmentet gir 2 745 600 kr i året (1B).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a) Anlegg Nordlys må vinne i året: 2 745 600 / 499 200, én desimal</t>
   </si>
   <si>
     <t xml:space="preserve">anlegg</t>
   </si>
   <si>
-    <t xml:space="preserve">b) Montørtimer i året: anlegg × 48 timer</t>
+    <t xml:space="preserve">b) Montørtimer i året: anlegg × 204 timer</t>
   </si>
   <si>
     <t xml:space="preserve">timer</t>
   </si>
   <si>
-    <t xml:space="preserve">c) Salgsinntekt med borettslagene i tillegg: 22 400 000 + 1 584 000</t>
+    <t xml:space="preserve">c) Salgsinntekt med borettslagene i tillegg: 22 400 000 + 2 745 600</t>
   </si>
   <si>
     <t xml:space="preserve">d) Borettslagenes andel av den nye salgsinntekten, i prosent med én desimal</t>
@@ -478,25 +478,25 @@
     <t xml:space="preserve">1B c) Salgsverdi i segmentet</t>
   </si>
   <si>
-    <t xml:space="preserve">528 × 12 000 = 6 336 000 kr</t>
+    <t xml:space="preserve">528 × 20 800 = 10 982 400 kr</t>
   </si>
   <si>
     <t xml:space="preserve">1B d) Per år</t>
   </si>
   <si>
-    <t xml:space="preserve">6 336 000 / 4 = 1 584 000 kr</t>
+    <t xml:space="preserve">10 982 400 / 4 = 2 745 600 kr</t>
   </si>
   <si>
     <t xml:space="preserve">1B e) Andel av salgsinntekten</t>
   </si>
   <si>
-    <t xml:space="preserve">1 584 000 / 22 400 000 = 7,07 %, avrundet 7 %</t>
+    <t xml:space="preserve">2 745 600 / 22 400 000 = 12,26 %, avrundet 12 %</t>
   </si>
   <si>
     <t xml:space="preserve">1B f) Montørtimer per år</t>
   </si>
   <si>
-    <t xml:space="preserve">528 × 2 = 1 056 timer, / 4 = 264 timer (1,8 % av 14 400)</t>
+    <t xml:space="preserve">528 × 8,5 = 4 488 timer, / 4 = 1 122 timer (7,8 % av 14 400)</t>
   </si>
   <si>
     <t xml:space="preserve">1B g) Fjell: bytter i året</t>
@@ -508,31 +508,31 @@
     <t xml:space="preserve">1B h) Fjell: andel av timene</t>
   </si>
   <si>
-    <t xml:space="preserve">90 × 6 = 540 timer. 540 / 3 500 = 15,4 %</t>
+    <t xml:space="preserve">90 × 14 = 1 260 timer. 1 260 / 3 500 = 36,0 %</t>
   </si>
   <si>
     <t xml:space="preserve">1B Kravene: borettslag</t>
   </si>
   <si>
-    <t xml:space="preserve">Oppfylt på alle fire: telt og antatt, innenfor kjøreavstand, 1 584 000 kr i året, 264 timer</t>
+    <t xml:space="preserve">Oppfylt på alle fire: telt og antatt, innenfor kjøreavstand, 2 745 600 kr i året, 1 122 timer</t>
   </si>
   <si>
     <t xml:space="preserve">1B Kravene: alle med elbil i Oslo</t>
   </si>
   <si>
-    <t xml:space="preserve">Målbart og stort nok, men ikke tilgjengelig (12 montører på ett sted) og ikke tilpasset kapasiteten (14 400 timer er brukt opp)</t>
+    <t xml:space="preserve">Målbart og stort nok, men ikke tilgjengelig (12 montører på ett sted) og ikke tilpasset kapasiteten (full kalender på prosjekt)</t>
   </si>
   <si>
     <t xml:space="preserve">1B Stort nok?</t>
   </si>
   <si>
-    <t xml:space="preserve">Ja: 1 584 000 kr er over idrettslagenes 600 000 og husstandenes 1 450 000. Boka: det største segmentet er ikke alltid det mest lønnsomme</t>
+    <t xml:space="preserve">Ja: 2 745 600 kr er over idrettslagenes 600 000 og husstandenes 1 450 000. Boka: det største segmentet er ikke alltid det mest lønnsomme</t>
   </si>
   <si>
     <t xml:space="preserve">1C Del 1: Strategiene</t>
   </si>
   <si>
-    <t xml:space="preserve">Én prisliste til alle: udifferensiert. Serviceavtale, styretilbud, anbudsteam: differensiert. Fjell, bare eneboliger før 1980: konsentrert. Tom, alt på totalentreprenørene: konsentrert. Samme brosjyre til alle: udifferensiert</t>
+    <t xml:space="preserve">Én prisliste til alle: udifferensiert. Serviceavtale, styretilbud, anbudsteam: differensiert. Fjell, bare eneboliger før 1980: konsentrert. Ronny, alt på totalentreprenørene: konsentrert. Samme brosjyre til alle: udifferensiert</t>
   </si>
   <si>
     <t xml:space="preserve">1C Del 2: Kriteriene</t>
@@ -544,31 +544,31 @@
     <t xml:space="preserve">1C a) Anlegg i året</t>
   </si>
   <si>
-    <t xml:space="preserve">1 584 000 / 288 000 = 5,5 anlegg (ett anlegg: 24 ladepunkt × 12 000 kr)</t>
+    <t xml:space="preserve">2 745 600 / 499 200 = 5,5 anlegg (ett anlegg: 24 ladepunkt × 20 800 kr)</t>
   </si>
   <si>
     <t xml:space="preserve">1C b) Montørtimer i året</t>
   </si>
   <si>
-    <t xml:space="preserve">5,5 × 48 = 264 timer</t>
+    <t xml:space="preserve">5,5 × 204 = 1 122 timer</t>
   </si>
   <si>
     <t xml:space="preserve">1C c) Salgsinntekt med borettslagene</t>
   </si>
   <si>
-    <t xml:space="preserve">22 400 000 + 1 584 000 = 23 984 000 kr</t>
+    <t xml:space="preserve">22 400 000 + 2 745 600 = 25 145 600 kr</t>
   </si>
   <si>
     <t xml:space="preserve">1C d) Borettslagenes andel</t>
   </si>
   <si>
-    <t xml:space="preserve">1 584 000 / 23 984 000 = 6,6 %, avrundet 7</t>
+    <t xml:space="preserve">2 745 600 / 25 145 600 = 10,9 %, avrundet 11</t>
   </si>
   <si>
     <t xml:space="preserve">1C Del 4: Anbefalingen</t>
   </si>
   <si>
-    <t xml:space="preserve">To målgrupper, for eksempel borettslagene (1 584 000 kr, 264 timer, består alle fire krav) og næringskundene (responstid). Differensiert: tre tilbud. Byggherrene beholdes med færre og større jobber; husstander og idrettslag tas når de kommer. Velger du byggherrene og kommunen: si hva lærlingkravet betyr, og hvorfor det største segmentet ikke er det mest lønnsomme</t>
+    <t xml:space="preserve">To målgrupper, for eksempel borettslagene (2 745 600 kr, 1 122 timer, består alle fire krav) og næringskundene (responstid). Differensiert: tre tilbud. Byggherrene beholdes med færre og større jobber; husstander og idrettslag tas når de kommer. Velger du byggherrene og kommunen: si hva lærlingkravet betyr, og hvorfor det største segmentet ikke er det mest lønnsomme</t>
   </si>
 </sst>
 </file>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="C16" s="12"/>
       <c r="G16" s="13" t="str">
-        <f aca="false">IF(C16="","Velg i nedtrekksmenyen.",IF(C16="Demografisk","Riktig. Boligen hører til bosted, et av bokas seks demografiske kriterier. Byggeåret kan telles, og et hus fra før 1980 har ofte et sikringsskap som må byttes.","Ikke riktig. Boligen hører til bosted, et av bokas seks demografiske kriterier. Byggeåret kan telles, og et hus fra før 1980 har ofte et sikringsskap som må byttes."))</f>
+        <f aca="false">IF(C16="","Velg i nedtrekksmenyen.",IF(C16="Demografisk","Riktig. Boligen hører til bosted, et av bokas seks demografiske kriterier. Byggeåret kan telles, og eldre hus har ofte skrusikringer uten jordfeilvern og trenger nytt sikringsskap.","Ikke riktig. Boligen hører til bosted, et av bokas seks demografiske kriterier. Byggeåret kan telles, og eldre hus har ofte skrusikringer uten jordfeilvern og trenger nytt sikringsskap."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
       <c r="Z16" s="6" t="s">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C27" s="12"/>
       <c r="G27" s="13" t="str">
-        <f aca="false">IF(C27="","Velg i nedtrekksmenyen.",IF(C27="Ja","Riktig. Et hus fra før 1980 har ofte et sikringsskap som må byttes. Det er et behov, og byggeåret kan telles.","Ikke riktig. Et hus fra før 1980 har ofte et sikringsskap som må byttes. Det er et behov, og byggeåret kan telles."))</f>
+        <f aca="false">IF(C27="","Velg i nedtrekksmenyen.",IF(C27="Ja","Riktig. Eldre hus har ofte skrusikringer uten jordfeilvern og trenger nytt sikringsskap. Det er et behov, og byggeåret kan telles.","Ikke riktig. Eldre hus har ofte skrusikringer uten jordfeilvern og trenger nytt sikringsskap. Det er et behov, og byggeåret kan telles."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
       <c r="Z27" s="6" t="s">
@@ -2246,7 +2246,7 @@
         <v>63</v>
       </c>
       <c r="C15" s="21" t="n">
-        <v>12000</v>
+        <v>20800</v>
       </c>
       <c r="Z15" s="6" t="s">
         <v>51</v>
@@ -2268,7 +2268,7 @@
         <v>65</v>
       </c>
       <c r="C17" s="21" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2342,7 +2342,7 @@
         <v>74</v>
       </c>
       <c r="G26" s="13" t="str">
-        <f aca="false">IF(C26="","Skriv svaret i den gule cellen.",IF(C26=(22*60*0.4*12000),"Riktig.",IF(ABS(C26-(22*60*12000))&lt;=0,"Du har ganget alle plassene med prisen. Bare de 528 som mangler ladepunkt, er et salg.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
+        <f aca="false">IF(C26="","Skriv svaret i den gule cellen.",IF(C26=(22*60*0.4*20800),"Riktig.",IF(ABS(C26-(22*60*20800))&lt;=0,"Du har ganget alle plassene med prisen. Bare de 528 som mangler ladepunkt, er et salg.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
         <v>76</v>
       </c>
       <c r="G27" s="13" t="str">
-        <f aca="false">IF(C27="","Skriv svaret i den gule cellen.",IF(C27=(22*60*0.4*12000/4),"Riktig.",IF(ABS(C27-(22*60*0.4*12000))&lt;=0,"Det er hele salgsverdien. Styrene bygger ut over fire år; del på 4.",IF(ABS(C27-(22*60*0.4*12000*4))&lt;=0,"Du har ganget med 4. Salgsverdien skal deles på årene, ikke ganges.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
+        <f aca="false">IF(C27="","Skriv svaret i den gule cellen.",IF(C27=(22*60*0.4*20800/4),"Riktig.",IF(ABS(C27-(22*60*0.4*20800))&lt;=0,"Det er hele salgsverdien. Styrene bygger ut over fire år; del på 4.",IF(ABS(C27-(22*60*0.4*20800*4))&lt;=0,"Du har ganget med 4. Salgsverdien skal deles på årene, ikke ganges.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
         <v>78</v>
       </c>
       <c r="G28" s="13" t="str">
-        <f aca="false">IF(C28="","Skriv svaret i den gule cellen.",IF(ABS(C28-(ROUND(22*60*0.4*12000/4/22400000*100,0)))&lt;=0.5,"Riktig.",IF(ABS(C28-(ROUND(22*60*0.4*12000/22400000*100,0)))&lt;=0.5,"Du har regnet andelen av hele salgsverdien, 6 336 000. Bruk tallet per år, 1 584 000.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
+        <f aca="false">IF(C28="","Skriv svaret i den gule cellen.",IF(ABS(C28-(ROUND(22*60*0.4*20800/4/22400000*100,0)))&lt;=0.5,"Riktig.",IF(ABS(C28-(ROUND(22*60*0.4*20800/22400000*100,0)))&lt;=0.5,"Du har regnet andelen av hele salgsverdien, 10 982 400. Bruk tallet per år, 2 745 600.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         <v>80</v>
       </c>
       <c r="G29" s="13" t="str">
-        <f aca="false">IF(C29="","Skriv svaret i den gule cellen.",IF(C29=(22*60*0.4*2/4),"Riktig.",IF(ABS(C29-(22*60*0.4*2))&lt;=0,"Det er timene for alle fire årene. Del på 4.",IF(ABS(C29-(22*60*0.4/4))&lt;=0,"Du har glemt at hvert ladepunkt tar 2 timer.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
+        <f aca="false">IF(C29="","Skriv svaret i den gule cellen.",IF(C29=(22*60*0.4*8.5/4),"Riktig.",IF(ABS(C29-(22*60*0.4*8.5))&lt;=0,"Det er timene for alle fire årene. Del på 4.",IF(ABS(C29-(22*60*0.4/4))&lt;=0,"Du har glemt at hvert ladepunkt i et felles anlegg tar 8,5 timer.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
         <v>78</v>
       </c>
       <c r="G32" s="13" t="str">
-        <f aca="false">IF(C32="","Skriv svaret i den gule cellen.",IF(ABS(C32-(ROUND(4000*0.45*0.05*6/3500*100,1)))&lt;=0.05,"Riktig.",IF(ABS(C32-(ROUND(4000*0.45*0.05/3500*100,1)))&lt;=0.05,"Du har delt bytter på timer. Hvert bytte tar 6 timer; gang først med 6.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
+        <f aca="false">IF(C32="","Skriv svaret i den gule cellen.",IF(ABS(C32-(ROUND(4000*0.45*0.05*14/3500*100,1)))&lt;=0.05,"Riktig.",IF(ABS(C32-(ROUND(4000*0.45*0.05/3500*100,1)))&lt;=0.05,"Du har delt bytter på timer. Hvert bytte tar 14 timer; gang først med 14.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="C37" s="12"/>
       <c r="G37" s="13" t="str">
-        <f aca="false">IF(C37="","Velg i nedtrekksmenyen.",IF(C37="Oppfylt","Riktig. 1 584 000 kr i året er mer enn idrettslagene (600 000) og mer enn husstandene (1 450 000). Over et rimelig minstemål.","Ikke riktig. 1 584 000 kr i året er mer enn idrettslagene (600 000) og mer enn husstandene (1 450 000). Over et rimelig minstemål."))</f>
+        <f aca="false">IF(C37="","Velg i nedtrekksmenyen.",IF(C37="Oppfylt","Riktig. 2 745 600 kr i året er mer enn idrettslagene (600 000) og mer enn husstandene (1 450 000). Over et rimelig minstemål.","Ikke riktig. 2 745 600 kr i året er mer enn idrettslagene (600 000) og mer enn husstandene (1 450 000). Over et rimelig minstemål."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="C38" s="12"/>
       <c r="G38" s="13" t="str">
-        <f aca="false">IF(C38="","Velg i nedtrekksmenyen.",IF(C38="Oppfylt","Riktig. 264 timer i året er 1,8 % av 14 400. Nordlys har teknikken og folkene, og kan bygge trinnvis.","Ikke riktig. 264 timer i året er 1,8 % av 14 400. Nordlys har teknikken og folkene, og kan bygge trinnvis."))</f>
+        <f aca="false">IF(C38="","Velg i nedtrekksmenyen.",IF(C38="Oppfylt","Riktig. 1 122 timer i året er 7,8 % av 14 400, under det én montør fakturerer (1 200). Prosjekt har full kalender, så timene må tas fra et annet segment, for eksempel byggherrene, eller dekkes med én ny montør. Anleggene kan planlegges og bygges trinnvis.","Ikke riktig. 1 122 timer i året er 7,8 % av 14 400, under det én montør fakturerer (1 200). Prosjekt har full kalender, så timene må tas fra et annet segment, for eksempel byggherrene, eller dekkes med én ny montør. Anleggene kan planlegges og bygges trinnvis."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="C44" s="12"/>
       <c r="G44" s="13" t="str">
-        <f aca="false">IF(C44="","Velg i nedtrekksmenyen.",IF(C44="Ikke oppfylt","Riktig. 14 400 timer er brukt opp. Nordlys kan ikke levere mengden til rett tid til hele Oslo. Avgrens segmentet i stedet.","Ikke riktig. 14 400 timer er brukt opp. Nordlys kan ikke levere mengden til rett tid til hele Oslo. Avgrens segmentet i stedet."))</f>
+        <f aca="false">IF(C44="","Velg i nedtrekksmenyen.",IF(C44="Ikke oppfylt","Riktig. Kalenderen er full på prosjekt, og 12 montører når ikke hele Oslo. Nordlys kan ikke levere mengden til rett tid. Avgrens segmentet i stedet.","Ikke riktig. Kalenderen er full på prosjekt, og 12 montører når ikke hele Oslo. Nordlys kan ikke levere mengden til rett tid. Avgrens segmentet i stedet."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
     </row>
     <row r="50" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="15" t="str">
-        <f aca="false">IF(LEN(B47)&lt;40,"",IF(AND(ISNUMBER(SEARCH("idrettslag",B47)),ISNUMBER(SEARCH("lønnsom",B47))),"Bra: du sammenlikner med idrettslagene og har med bokas poeng om at det største segmentet ikke alltid er det mest lønnsomme.",IF(OR(ISNUMBER(SEARCH("idrettslag",B47)),ISNUMBER(SEARCH("lønnsom",B47))),"Du er på sporet. Ta med både sammenlikningen med idrettslagene (600 000 kr) og det boka sier om at det største segmentet ikke alltid er det mest lønnsomme.","Tips: 1 584 000 kr i året er mer enn idrettslagene med 600 000 og mer enn husstandene med 1 450 000, så det er over et rimelig minstemål. Og boka: det største segmentet, byggherrene, er ikke alltid det mest lønnsomme, for der er konkurransen størst og prisene under press.")))</f>
+        <f aca="false">IF(LEN(B47)&lt;40,"",IF(AND(ISNUMBER(SEARCH("idrettslag",B47)),ISNUMBER(SEARCH("lønnsom",B47))),"Bra: du sammenlikner med idrettslagene og har med bokas poeng om at det største segmentet ikke alltid er det mest lønnsomme.",IF(OR(ISNUMBER(SEARCH("idrettslag",B47)),ISNUMBER(SEARCH("lønnsom",B47))),"Du er på sporet. Ta med både sammenlikningen med idrettslagene (600 000 kr) og det boka sier om at det største segmentet ikke alltid er det mest lønnsomme.","Tips: 2 745 600 kr i året er mer enn idrettslagene med 600 000 og mer enn husstandene med 1 450 000, så det er over et rimelig minstemål. Og boka: det største segmentet, byggherrene, er ikke alltid det mest lønnsomme, for der er konkurransen størst og prisene under press.")))</f>
         <v/>
       </c>
       <c r="C50" s="15"/>
@@ -2564,7 +2564,7 @@
     </row>
     <row r="52" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="17" t="str">
-        <f aca="false">IF(C51="JA","Hint: a: 22 × 60 = 1 320. b: 1 320 × 0,40 = 528. c: 528 × 12 000 = 6 336 000. d: 6 336 000 / 4 = 1 584 000. e: 1 584 000 / 22 400 000 = 7,07 %, avrundet 7. f: 528 × 2 / 4 = 264. g: 4 000 × 0,45 × 0,05 = 90. h: 90 × 6 = 540 timer, 540 / 3 500 = 15,4 %.","")</f>
+        <f aca="false">IF(C51="JA","Hint: a: 22 × 60 = 1 320. b: 1 320 × 0,40 = 528. c: 528 × 20 800 = 10 982 400. d: 10 982 400 / 4 = 2 745 600. e: 2 745 600 / 22 400 000 = 12,26 %, avrundet 12. f: 528 × 8,5 / 4 = 1 122. g: 4 000 × 0,45 × 0,05 = 90. h: 90 × 14 = 1 260 timer, 1 260 / 3 500 = 36,0 %.","")</f>
         <v/>
       </c>
       <c r="C52" s="17"/>
@@ -2839,7 +2839,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
         <v>95</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>109</v>
       </c>
       <c r="C19" s="21" t="n">
-        <v>1584000</v>
+        <v>2745600</v>
       </c>
       <c r="D19" s="26" t="s">
         <v>110</v>
@@ -3236,7 +3236,7 @@
         <v>126</v>
       </c>
       <c r="G39" s="13" t="str">
-        <f aca="false">IF(C39="","Skriv svaret i den gule cellen.",IF(ABS(C39-(ROUND(1584000/288000,1)))&lt;=0.05,"Riktig.",IF(ABS(C39-(22))&lt;=0.05,"Du har svart alle 22 borettslagene. De bygger ut over fire år; 1 584 000 kr i året er 5,5 anlegg.",IF(ABS(C39-(ROUND(6336000/288000,1)))&lt;=0.05,"Du har delt hele salgsverdien, 6 336 000, på ett anlegg. Det er 22 anlegg over fire år. Per år: 1 584 000 / 288 000.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
+        <f aca="false">IF(C39="","Skriv svaret i den gule cellen.",IF(ABS(C39-(ROUND(2745600/499200,1)))&lt;=0.05,"Riktig.",IF(ABS(C39-(22))&lt;=0.05,"Du har svart alle 22 borettslagene. De bygger ut over fire år; 2 745 600 kr i året er 5,5 anlegg.",IF(ABS(C39-(ROUND(10982400/499200,1)))&lt;=0.05,"Du har delt hele salgsverdien, 10 982 400, på ett anlegg. Det er 22 anlegg over fire år. Per år: 2 745 600 / 499 200.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
         <v>128</v>
       </c>
       <c r="G40" s="13" t="str">
-        <f aca="false">IF(C40="","Skriv svaret i den gule cellen.",IF(ABS(C40-(ROUND(1584000/288000*48,0)))&lt;=1,"Riktig.",IF(ABS(C40-(48))&lt;=1,"Det er timene for ett anlegg. Gang med 5,5 anlegg i året.",IF(ABS(C40-(22*48))&lt;=1,"Du har tatt alle 22 anleggene. Det er over fire år; per år er det 5,5 anlegg.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
+        <f aca="false">IF(C40="","Skriv svaret i den gule cellen.",IF(ABS(C40-(ROUND(2745600/499200*204,0)))&lt;=1,"Riktig.",IF(ABS(C40-(204))&lt;=1,"Det er timene for ett anlegg. Gang med 5,5 anlegg i året.",IF(ABS(C40-(22*204))&lt;=1,"Du har tatt alle 22 anleggene. Det er over fire år; per år er det 5,5 anlegg.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
         <v>74</v>
       </c>
       <c r="G41" s="13" t="str">
-        <f aca="false">IF(C41="","Skriv svaret i den gule cellen.",IF(C41=(22400000+1584000),"Riktig.",IF(ABS(C41-(22400000+6336000))&lt;=0,"Du har lagt til hele salgsverdien over fire år. Per år er det 1 584 000.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
+        <f aca="false">IF(C41="","Skriv svaret i den gule cellen.",IF(C41=(22400000+2745600),"Riktig.",IF(ABS(C41-(22400000+10982400))&lt;=0,"Du har lagt til hele salgsverdien over fire år. Per år er det 2 745 600.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
         <v>78</v>
       </c>
       <c r="G42" s="13" t="str">
-        <f aca="false">IF(C42="","Skriv svaret i den gule cellen.",IF(ABS(C42-(ROUND(1584000/(22400000+1584000)*100,1)))&lt;=0.05,"Riktig.",IF(ABS(C42-(ROUND(1584000/22400000*100,1)))&lt;=0.05,"Du har delt på den gamle salgsinntekten, 22 400 000. Borettslagene kommer i tillegg; del på 23 984 000.",IF(ABS(C42-(ROUND(6336000/(22400000+1584000)*100,1)))&lt;=0.05,"Du har brukt hele salgsverdien, 6 336 000. Bruk tallet per år, 1 584 000.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
+        <f aca="false">IF(C42="","Skriv svaret i den gule cellen.",IF(ABS(C42-(ROUND(2745600/(22400000+2745600)*100,1)))&lt;=0.05,"Riktig.",IF(ABS(C42-(ROUND(2745600/22400000*100,1)))&lt;=0.05,"Du har delt på den gamle salgsinntekten, 22 400 000. Borettslagene kommer i tillegg; del på 25 145 600.",IF(ABS(C42-(ROUND(10982400/(22400000+2745600)*100,1)))&lt;=0.05,"Du har brukt hele salgsverdien, 10 982 400. Bruk tallet per år, 2 745 600.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
     </row>
     <row r="48" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="15" t="str">
-        <f aca="false">IF(LEN(B45)&lt;40,"",IF(AND(ISNUMBER(SEARCH("ifferensiert",B45)),ISNUMBER(SEARCH("krav",B45))),"Bra: du navngir strategien, tester mot kravene og sier hva som skjer med resten. Sjekk at du også har med et tall (1 584 000 kr, 264 timer eller 47 %).",IF(OR(ISNUMBER(SEARCH("ifferensiert",B45)),ISNUMBER(SEARCH("krav",B45))),"Du er på sporet. Navngi strategien (differensiert eller konsentrert), og vis at du har testet målgruppene mot de fire kravene.","Tips: et godt svar velger for eksempel borettslagene (1 584 000 kr, 264 timer, består alle fire krav) og næringskundene (responstid), kaller strategien differensiert, og sier at byggherrene beholdes med færre og større jobber mens husstander og idrettslag tas når de kommer.")))</f>
+        <f aca="false">IF(LEN(B45)&lt;40,"",IF(AND(ISNUMBER(SEARCH("ifferensiert",B45)),ISNUMBER(SEARCH("krav",B45))),"Bra: du navngir strategien, tester mot kravene og sier hva som skjer med resten. Sjekk at du også har med et tall (2 745 600 kr, 1 122 timer eller 47 %).",IF(OR(ISNUMBER(SEARCH("ifferensiert",B45)),ISNUMBER(SEARCH("krav",B45))),"Du er på sporet. Navngi strategien (differensiert eller konsentrert), og vis at du har testet målgruppene mot de fire kravene.","Tips: et godt svar velger for eksempel borettslagene (2 745 600 kr, 1 122 timer, består alle fire krav) og næringskundene (responstid), kaller strategien differensiert, og sier at byggherrene beholdes med færre og større jobber mens husstander og idrettslag tas når de kommer.")))</f>
         <v/>
       </c>
       <c r="C48" s="15"/>
@@ -3332,7 +3332,7 @@
     </row>
     <row r="50" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="17" t="str">
-        <f aca="false">IF(C49="JA","Hint: a: 1 584 000 / 288 000 = 5,5 anlegg. b: 5,5 × 48 = 264 timer. c: 22 400 000 + 1 584 000 = 23 984 000. d: 1 584 000 / 23 984 000 = 6,6 %. Strategiene: samme tilbud til alle er udifferensiert, ulike tilbud til ulike grupper er differensiert, alt på ett segment er konsentrert.","")</f>
+        <f aca="false">IF(C49="JA","Hint: a: 2 745 600 / 499 200 = 5,5 anlegg. b: 5,5 × 204 = 1 122 timer. c: 22 400 000 + 2 745 600 = 25 145 600. d: 2 745 600 / 25 145 600 = 10,9 %. Strategiene: samme tilbud til alle er udifferensiert, ulike tilbud til ulike grupper er differensiert, alt på ett segment er konsentrert.","")</f>
         <v/>
       </c>
       <c r="C50" s="17"/>
@@ -3620,7 +3620,7 @@
         <v>147</v>
       </c>
       <c r="C11" s="30" t="n">
-        <v>6336000</v>
+        <v>10982400</v>
       </c>
       <c r="D11" s="29" t="s">
         <v>148</v>
@@ -3631,7 +3631,7 @@
         <v>149</v>
       </c>
       <c r="C12" s="30" t="n">
-        <v>1584000</v>
+        <v>2745600</v>
       </c>
       <c r="D12" s="29" t="s">
         <v>150</v>
@@ -3642,7 +3642,7 @@
         <v>151</v>
       </c>
       <c r="C13" s="30" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D13" s="29" t="s">
         <v>152</v>
@@ -3653,7 +3653,7 @@
         <v>153</v>
       </c>
       <c r="C14" s="30" t="n">
-        <v>264</v>
+        <v>1122</v>
       </c>
       <c r="D14" s="29" t="s">
         <v>154</v>
@@ -3675,7 +3675,7 @@
         <v>157</v>
       </c>
       <c r="C16" s="30" t="n">
-        <v>15.4</v>
+        <v>36</v>
       </c>
       <c r="D16" s="29" t="s">
         <v>158</v>
@@ -3742,7 +3742,7 @@
         <v>171</v>
       </c>
       <c r="C23" s="30" t="n">
-        <v>264</v>
+        <v>1122</v>
       </c>
       <c r="D23" s="29" t="s">
         <v>172</v>
@@ -3753,7 +3753,7 @@
         <v>173</v>
       </c>
       <c r="C24" s="30" t="n">
-        <v>23984000</v>
+        <v>25145600</v>
       </c>
       <c r="D24" s="29" t="s">
         <v>174</v>
@@ -3764,7 +3764,7 @@
         <v>175</v>
       </c>
       <c r="C25" s="30" t="n">
-        <v>6.6</v>
+        <v>10.9</v>
       </c>
       <c r="D25" s="29" t="s">
         <v>176</v>

--- a/pensum/ma05/MA05_Markedssegmentering_Oppgaver_v6.xlsx
+++ b/pensum/ma05/MA05_Markedssegmentering_Oppgaver_v6.xlsx
@@ -1167,7 +1167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1192,27 +1192,27 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
@@ -1399,7 +1399,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="10" t="s">
         <v>29</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="26" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
@@ -2411,7 +2411,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="34" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="10" t="s">
         <v>84</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="40" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="10" t="s">
         <v>89</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="60.75" customHeight="true" r="22" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="9" t="s">
         <v>111</v>
       </c>
@@ -3071,7 +3071,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="24" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="10" t="s">
         <v>112</v>
       </c>
@@ -3154,7 +3154,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="31" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="10" t="s">
         <v>118</v>
       </c>
@@ -3167,7 +3167,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="32" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="11" t="s">
         <v>119</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="33" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="11" t="s">
         <v>120</v>
       </c>
@@ -3217,7 +3217,7 @@
       <c r="F37" s="8"/>
       <c r="G37" s="8"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="38" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="9" t="s">
         <v>124</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="60.75" customHeight="true" r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="29" t="s">
         <v>137</v>
       </c>
